--- a/chapters/12/core/AIHE-D02/supp/AIHE-EX14/xlsx/AIHE-EX14_workbook.xlsx
+++ b/chapters/12/core/AIHE-D02/supp/AIHE-EX14/xlsx/AIHE-EX14_workbook.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" r:id="R45aae18c62234710"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Template" sheetId="2" r:id="R80f44339e3ff436e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Worked_Example" sheetId="3" r:id="R62772c139bf14e8d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Dictionary" sheetId="4" r:id="Rf92bfacf9a3e4b19"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" r:id="R8afc7de818904f3f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Template" sheetId="2" r:id="R00e8c7c6170e4370"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Worked_Example" sheetId="3" r:id="Rfff84fd7e8764336"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Dictionary" sheetId="4" r:id="R6521ded552fc45b9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -34,7 +34,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="3">
+  <x:fills count="4">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -46,6 +46,11 @@
         <x:fgColor rgb="FF1F4E79"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF303236"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="2">
     <x:border/>
@@ -54,25 +59,17 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="22">
+  <x:cellXfs count="31">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0"/>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyAlignment="1">
-      <x:alignment/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyAlignment="1">
-      <x:alignment/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyAlignment="1">
-      <x:alignment/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyAlignment="1">
-      <x:alignment/>
-    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyAlignment="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyAlignment="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyAlignment="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
@@ -86,23 +83,34 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0"/>
-    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyAlignment="1">
-      <x:alignment/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyAlignment="1">
-      <x:alignment/>
-    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyAlignment="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0"/>
-    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyAlignment="1">
-      <x:alignment/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyAlignment="1">
-      <x:alignment/>
-    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyAlignment="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -336,7 +344,7 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="12" t="inlineStr">
+      <x:c r="A1" s="29" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">AIHE-EX14 — Final Board Recommendation Pack</x:t>
         </x:is>
@@ -481,37 +489,37 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="20" t="inlineStr">
+      <x:c r="A1" s="30" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Section</x:t>
         </x:is>
       </x:c>
-      <x:c r="B1" s="20" t="inlineStr">
+      <x:c r="B1" s="30" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Field</x:t>
         </x:is>
       </x:c>
-      <x:c r="C1" s="20" t="inlineStr">
+      <x:c r="C1" s="30" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Response / evidence</x:t>
         </x:is>
       </x:c>
-      <x:c r="D1" s="20" t="inlineStr">
+      <x:c r="D1" s="30" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Owner</x:t>
         </x:is>
       </x:c>
-      <x:c r="E1" s="20" t="inlineStr">
+      <x:c r="E1" s="30" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Due date</x:t>
         </x:is>
       </x:c>
-      <x:c r="F1" s="20" t="inlineStr">
+      <x:c r="F1" s="30" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Status</x:t>
         </x:is>
       </x:c>
-      <x:c r="G1" s="20" t="inlineStr">
+      <x:c r="G1" s="30" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Evidence link / note</x:t>
         </x:is>
@@ -741,37 +749,37 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="20" t="inlineStr">
+      <x:c r="A1" s="30" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Section</x:t>
         </x:is>
       </x:c>
-      <x:c r="B1" s="20" t="inlineStr">
+      <x:c r="B1" s="30" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Field</x:t>
         </x:is>
       </x:c>
-      <x:c r="C1" s="20" t="inlineStr">
+      <x:c r="C1" s="30" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Response / evidence</x:t>
         </x:is>
       </x:c>
-      <x:c r="D1" s="20" t="inlineStr">
+      <x:c r="D1" s="30" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Owner</x:t>
         </x:is>
       </x:c>
-      <x:c r="E1" s="20" t="inlineStr">
+      <x:c r="E1" s="30" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Due date</x:t>
         </x:is>
       </x:c>
-      <x:c r="F1" s="20" t="inlineStr">
+      <x:c r="F1" s="30" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Status</x:t>
         </x:is>
       </x:c>
-      <x:c r="G1" s="20" t="inlineStr">
+      <x:c r="G1" s="30" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Evidence link / note</x:t>
         </x:is>
@@ -1091,32 +1099,32 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="20" t="inlineStr">
+      <x:c r="A1" s="30" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Sheet</x:t>
         </x:is>
       </x:c>
-      <x:c r="B1" s="20" t="inlineStr">
+      <x:c r="B1" s="30" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Variable</x:t>
         </x:is>
       </x:c>
-      <x:c r="C1" s="20" t="inlineStr">
+      <x:c r="C1" s="30" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Type</x:t>
         </x:is>
       </x:c>
-      <x:c r="D1" s="20" t="inlineStr">
+      <x:c r="D1" s="30" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Allowed values / units</x:t>
         </x:is>
       </x:c>
-      <x:c r="E1" s="20" t="inlineStr">
+      <x:c r="E1" s="30" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Description</x:t>
         </x:is>
       </x:c>
-      <x:c r="F1" s="20" t="inlineStr">
+      <x:c r="F1" s="30" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Example</x:t>
         </x:is>
